--- a/fazendas.xlsx
+++ b/fazendas.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$B$7419</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterateDelta="1E-4"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>

--- a/fazendas.xlsx
+++ b/fazendas.xlsx
@@ -18,7 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Planilha1!$A$1:$B$7419</definedName>
   </definedNames>
-  <calcPr calcId="191029" iterateDelta="1E-4"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
